--- a/data/hardtail/Ridley Ignite GTX 2025.xlsx
+++ b/data/hardtail/Ridley Ignite GTX 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/hardtail/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58DC2ADA-E76E-5E41-8E6D-B94978B3ADE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D3A5246-8601-D944-B563-F06C2E849A20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3260" yWindow="500" windowWidth="25540" windowHeight="16700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -302,9 +302,6 @@
     <t>rigid</t>
   </si>
   <si>
-    <t xml:space="preserve">Kanzo Adventure  </t>
-  </si>
-  <si>
     <t>internal</t>
   </si>
   <si>
@@ -324,6 +321,9 @@
   </si>
   <si>
     <t>hardtail</t>
+  </si>
+  <si>
+    <t>Ignite GTX</t>
   </si>
 </sst>
 </file>
@@ -697,7 +697,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -721,7 +721,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -729,7 +729,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -737,7 +737,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>8</v>
@@ -1107,7 +1107,7 @@
         <v>84</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
@@ -1171,7 +1171,7 @@
         <v>55</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
@@ -1263,7 +1263,7 @@
         <v>71</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
@@ -1291,7 +1291,7 @@
         <v>76</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
@@ -1299,7 +1299,7 @@
         <v>77</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
@@ -1312,7 +1312,7 @@
         <v>79</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
@@ -1338,7 +1338,7 @@
         <v>83</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
